--- a/questions.xlsx
+++ b/questions.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="السعودية" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="معلومات عامة" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="flagged" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="كاس العالم" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="flagged" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15302,6 +15303,7344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F333"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>السؤال</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>الجواب</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>النقاط</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>صورة السؤال</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>صورة الجواب</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ملاحظات أو أجوبة مقبولة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي فاز ببطولة كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>الأرجنتين</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أرجنتين / منتخب الأرجنتين</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأكثر تتويجاً بكأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>البرازيل</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب البرازيل / السيلساو</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>في أي دولة أُقيمت نهائيات كأس العالم عام 2022م؟</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>قطر</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>كم سنة تفصل بين كل نسخة من كأس العالم والنسخة التي تليها؟</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4 سنوات</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أربع سنوات / 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الشهير للهدف الذي سجله دييغو مارادونا بيده في مرمى إنجلترا في كأس العالم 1986م؟</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>يد الله</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: يد الإله / Hand of God</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>من هو اللاعب الفائز بجائزة الكرة الذهبية لأفضل لاعب في كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ليونيل ميسي</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ميسي</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب السعودي الذي سجل هدفاً شهيراً في مرمى بلجيكا بعد مراوغة طويلة في كأس العالم 1994م؟</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>سعيد العويران</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: العويران</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ما الجهة التي تنظم بطولة كأس العالم وتدير كرة القدم على المستوى الدولي؟</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>الفيفا</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الاتحاد الدولي لكرة القدم / FIFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي فاز بكأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>فرنسا</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب فرنسا / الديوك</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب البرازيل الملقب بـ(ملك كرة القدم) والذي فاز بكأس العالم ثلاث مرات؟</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>بيليه</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بيلي / بليه / Pelé</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب فرنسا الذي سجل ثلاثة أهداف في نهائي كأس العالم 2022م رغم خسارة فريقه؟</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>كيليان مبابي</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مبابي / مباپي</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي هزم البرازيل بسبعة أهداف مقابل هدف في نصف نهائي كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ألمانيا</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب ألمانيا / المانشافت</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب فرنسا الذي طُرد في نهائي كأس العالم 2006م بعد أن نطح أحد لاعبي الفريق المنافس بصدره؟</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>زين الدين زيدان</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: زيدان / زيزو</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب العربي الذي بلغ الدور نصف النهائي في كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب المغرب / أسود الأطلس</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم المختصر لتقنية الفيديو التي يستعين بها الحكم لمراجعة قراراته، وطُبّقت لأول مرة في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>الفار</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: VAR / حكم الفيديو المساعد</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الجائزة التي تُمنح لأكثر لاعب تسجيلاً للأهداف في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>الحذاء الذهبي</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الطريقة التي تُحسم بها المباراة بعد التعادل في الوقتين الأصلي والإضافي في أدوار خروج المغلوب؟</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ركلات الترجيح</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ضربات الجزاء الترجيحية / ركلات الجزاء الترجيحية</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي هزم السعودية بخمسة أهداف دون رد في افتتاح كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>روسيا</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب روسيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي استضافت كأس العالم 2010م لتكون أول دولة في القارة السمراء تنظمه؟</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>جنوب أفريقيا</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: جنوب إفريقيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب السعودي الذي سجل هدف الفوز على الأرجنتين (2-1) في كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>سالم الدوسري</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الدوسري. سجّل صالح الشهري الهدف الأول وسالم الدوسري الهدف الثاني (هدف الفوز)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدرب الذي قاد المنتخب السعودي في كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>هيرفي رينارد</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رينارد / Hervé Renard</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أخرجه المغرب من ربع نهائي كأس العالم 2022م بهدف دون رد؟</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>البرتغال</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب البرتغال</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب مصر الذي سجل هدفاً في مرمى السعودية في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>محمد صلاح</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: صلاح / Mohamed Salah</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم البوق البلاستيكي الذي ارتبط بأجواء كأس العالم 2010م وبصوته المزعج؟</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>الفوفوزيلا</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فوفوزيلا / الفوفوزيلة / Vuvuzela</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المعدن الثمين الذي صُنعت منه كأس العالم الأصلية الحالية؟</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>الذهب</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ذهب / ذهب عيار 18 قيراطاً</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>كم مرة فازت الأرجنتين بكأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ثلاث مرات</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 3 / ثلاثة. الأعوام: 1978 و1986 و2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>في أي شهر أُقيمت المباراة النهائية لكأس العالم 2022م على غير المعتاد؟</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ديسمبر</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كانون الأول. أُقيمت يوم 18 ديسمبر 2022م</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب البرتغال الذي سجل ثلاثية في مرمى إسبانيا في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>كريستيانو رونالدو</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رونالدو / كريستيانو. انتهت المباراة 3-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي استضافت كأس العالم عام 1994م؟</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>الولايات المتحدة</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أمريكا / الولايات المتحدة الأمريكية</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم حارس مرمى المنتخب السعودي في كأس العالم 1994م؟</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>محمد الدعيع</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الدعيع / محمد عبدالله الدعيع</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب الأوروغواي الذي عُوقب بسبب عضّ منافسه في كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>لويس سواريز</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: سواريز / لويس سواريس / Luis Suárez</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أسلوب اللعب القائم على التمريرات القصيرة والاستحواذ الذي اشتهر به منتخب إسبانيا؟</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>تيكي تاكا</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: تكي تاكا / تيكا تاكا / Tiki-taka</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ما الشكل الذي يحمله اللاعبان المجسّدان في أعلى كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>الكرة الأرضية</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الأرض / الكرة الأرضية / الكرة الارضية</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي شاركت الولايات المتحدة والمكسيك في استضافة كأس العالم 2026م؟</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>كندا</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كندا. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة العربية التي أكد الفيفا في ديسمبر 2024م أنها ستستضيف كأس العالم 2034م؟</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>السعودية</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: المملكة العربية السعودية. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 2026م بالفوز 1-0 في الوقت الإضافي؟</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>إسبانيا</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إسبانيا / أسبانيا. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب العربي الذي تأهل لأول مرة في تاريخه إلى كأس العالم 2026م؟</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>الأردن</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الأردن / النشامى. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>كم منتخباً يتأهل من كل مجموعة إلى دور الـ16 في نظام الـ32 منتخباً؟</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخبان / اثنان / 2 منتخبين</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم رئيس الفيفا الذي انتُخب عام 2016م خلفاً لسيب بلاتر؟</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>جياني إنفانتينو</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: إنفانتينو / جاني إنفانتينو / Gianni Infantino</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم هداف منتخب ساحل العاج التاريخي وقائده الذي قاده إلى أول مشاركة في كأس العالم عام 2006م؟</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ديدييه دروغبا</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: دروغبا / ديدييه دروجبا / Didier Drogba</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الرداء العربي الأسود الذي ألبسه أمير قطر لميسي قبل رفعه كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>البشت</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: المشلح / بشت / العباءة العربية</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>في أي قارة أُقيمت نسخة كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>آسيا</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: القارة الآسيوية</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>في أي شهر من السنة تنطلق نسخ كأس العالم عادةً باستثناء نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>يونيو</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: حزيران / June. انطلقت نسخ 2014 و2018 و2026 في يونيو</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المباراة التي تُلعب قبل النهائي بيوم واحد بين الخاسرين من الدور قبل الأخير؟</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>مباراة المركز الثالث</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مباراة تحديد المركز الثالث / مباراة المركزين الثالث والرابع</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي خسر معه ليونيل ميسي نهائي كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>الأرجنتين</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الأرجنتين</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>كم مباراة يلعبها كل منتخب في دور المجموعات؟</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>3 مباريات</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ثلاث مباريات / ثلاث</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 2006م بركلات الترجيح؟</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>إيطاليا</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إيطاليا / ايطاليا</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 1986م؟</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>الأرجنتين</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الأرجنتين</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم المنتخب البرتغالي الذي بلغ نصف نهائي كأس العالم واشتهر بانتقاله المثير للجدل إلى ريال مدريد عام 2000م؟</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>لويس فيغو</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فيغو / لويش فيغو / Luís Figo. شارك في نسخة 2006م</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 2014م بعد وقت إضافي؟</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ألمانيا</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب ألمانيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الشركة الألمانية المصنّعة للكرة الرسمية لكأس العالم منذ نسخة 1970م؟</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>أديداس</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: اديداس / Adidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الوحيد الذي شارك في جميع نسخ كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>البرازيل</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب البرازيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم البرازيل الذي غاب عن بقية كأس العالم 2014م بعد إصابة في فقرات الظهر في ربع النهائي؟</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>نيمار</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: نيمار جونيور / Neymar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب العربي الذي هزم فرنسا 1-0 في ختام دور المجموعات بكأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>تونس</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب تونس / نسور قرطاج</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم النجم الذي فاز بكأس العالم لأول مرة في مشاركته الخامسة عام 2022م؟</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ليونيل ميسي</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ميسي / Lionel Messi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 1998م على أرضه؟</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>فرنسا</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب فرنسا</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 2002م للمرة الخامسة؟</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>البرازيل</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب البرازيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 1970م وحصل على الكأس الأصلية نهائياً؟</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>البرازيل</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب البرازيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 1982م بقيادة باولو روسي؟</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>إيطاليا</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إيطاليا / ايطاليا</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>ما رقم القميص الذي اشتهر به كريستيانو رونالدو مع منتخب بلاده في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رقم 7 / سبعة / السابع</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب المضيف الذي أقصى إسبانيا بركلات الترجيح في ثمن نهائي كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>روسيا</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب روسيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم إنجلترا الذي طُرد في ثمن نهائي كأس العالم 1998م بعد ركلة على لاعب أرجنتيني؟</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ديفيد بيكهام</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بيكهام / David Beckham</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الأغنية الرسمية لكأس العالم 2010م التي غنتها المطربة الكولومبية شاكيرا؟</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>واكا واكا</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Waka Waka / هذه المرة لأفريقيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم الأرجنتين الراحل الذي قاد بلاده للقب كأس العالم 1986م وكان يُقارن دائماً بالبرازيلي بيليه؟</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>دييغو مارادونا</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مارادونا / Diego Maradona</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم النجم الفرنسي الذي سجل في نهائي كأس العالم 2018م وهو في التاسعة عشرة من عمره؟</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>كيليان مبابي</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مبابي / Kylian Mbappé</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم فرنسا من أصول جزائرية الذي سجل هدفين برأسه في نهائي كأس العالم 1998م؟</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>زين الدين زيدان</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: زيدان / Zinedine Zidane</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم مصر الذي غاب عن مباراة بلاده الأولى في كأس العالم 2018م بسبب إصابة في الكتف؟</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>محمد صلاح</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: صلاح / Mohamed Salah</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي استضافت أول نسخة من كأس العالم عام 1930م وفازت بها؟</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>الأوروغواي</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أوروغواي / أوروجواي / الأوروجواي</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي فاز بكأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>إسبانيا</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إسبانيا / أسبانيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم حارس المرمى الفائز بجائزة القفاز الذهبي لأفضل حارس في كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>إميليانو مارتينيز</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: إيميليانو مارتينيز / مارتينيز / ديبو مارتينيز</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب العربي الذي هزم ألمانيا الغربية 2-1 في دور المجموعات بكأس العالم 1982م؟</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>الجزائر</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الجزائر / محاربو الصحراء</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب منتخب إنجلترا الذي فاز بالحذاء الذهبي في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>هاري كين</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كين / Harry Kane. سجّل 6 أهداف</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المهاجم البرازيلي الذي سجل ثمانية أهداف وفاز بالحذاء الذهبي في كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>رونالدو</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رونالدو نازاريو / الظاهرة / رونالدو لويس نازاريو. لا يُقبل كريستيانو رونالدو</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أخرج السعودية من دور الـ16 في كأس العالم 1994م؟</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>السويد</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب السويد. انتهت المباراة 3-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم التميمة الرسمية لكأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>لعيب</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: لعّيب / La'eeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي حلّ ثالثاً في كأس العالم 1998م في أول مشاركة له؟</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>كرواتيا</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كرواتيا. فاز على هولندا 2-1 في مباراة المركز الثالث</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي فاز بكأس العالم 1966م على أرضه؟</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>إنجلترا</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إنجلترا / انجلترا</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي شاركت اليابان في استضافة كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>كوريا الجنوبية</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كوريا</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي خسر ثلاث نهائيات في كأس العالم دون أن يفوز بالبطولة حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>هولندا</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب هولندا / الطواحين. خسر نهائيات 1974 و1978 و2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول منتخب أفريقي يفوز بمباراة في نهائيات كأس العالم، وذلك على المكسيك عام 1978م؟</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>تونس</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب تونس / نسور قرطاج. فازت 3-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول منتخب عربي شارك في نهائيات كأس العالم عام 1934م؟</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب مصر</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم رئيس الفيفا الفرنسي الذي حملت الكأس الأصلية للبطولة اسمه حتى عام 1970م؟</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>جول ريميه</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: جول ريميت / ريميه / Jules Rimet</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الاستاد الذي خسرت فيه البرازيل أمام الأوروغواي المباراة الحاسمة لكأس العالم 1950م؟</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>استاد ماراكانا</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ماراكانا / ملعب ماراكانا</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الذي كان أول منتخب من قارته يبلغ ربع نهائي كأس العالم عام 1990م؟</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>الكاميرون</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الكاميرون / الأسود غير المروضة</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب السعودي الذي سجل أول هدف لمنتخب بلاده في تاريخ كأس العالم أمام هولندا عام 1994م؟</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>فؤاد أنور</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فؤاد أمين / فؤاد أنور أمين</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أسلوب اللعب القائم على تبادل المراكز بين اللاعبين الذي اشتُهر به منتخب هولندا في كأس العالم 1974م؟</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>الكرة الشاملة</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الكرة الكلية / كرة القدم الشاملة / Total Football</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>أي قارة فازت منتخباتها بأكبر عدد من نسخ كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>أوروبا</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: القارة الأوروبية. فازت منتخباتها بـ12 نسخة مقابل 10 لأمريكا الجنوبية</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الأخطبوط الذي اشتهر بتوقّع نتائج المباريات في كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>بول</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الأخطبوط بول / Paul</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>كم عدد المنتخبات التي شاركت في نسخة 2026م، وهي أول نسخة بهذا العدد؟</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 48 منتخباً / ثمانية وأربعون. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم منتخب هولندا الذي اشتُهر بحركة الاستدارة التي تحمل اسمه في كأس العالم 1974م، وكان يرتدي القميص رقم 14؟</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>يوهان كرويف</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كرويف / كرايف / يوهان كرايف / Johan Cruyff</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب كرواتيا الفائز بجائزة الكرة الذهبية لأفضل لاعب في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>لوكا مودريتش</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مودريتش / Luka Modrić</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المهاجم الأفريقي الذي اشتهر برقصة الراية الركنية بعد تسجيله الأهداف في كأس العالم 1990م؟</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>روجيه ميلا</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ميلا / روجر ميلا / Roger Milla</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب إيطاليا الذي أضاع ركلة الترجيح الأخيرة في نهائي كأس العالم 1994م؟</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>روبرتو باجيو</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: باجيو / روبيرتو باجيو / باجو / Roberto Baggio</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل هدف الفوز في الوقت الإضافي من نهائي كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>أندريس إنييستا</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: إنييستا / إنيستا / Andrés Iniesta. سجله في الدقيقة 116</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الذي فاز على حامل اللقب في افتتاح كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>السنغال</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب السنغال / أسود التيرانغا</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الذي حُرم من نصف نهائي كأس العالم 2010م بعد لمسة يد من لاعب الأوروغواي في آخر لحظات الوقت الإضافي؟</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>غانا</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب غانا / النجوم السوداء. خسر بركلات الترجيح في ربع النهائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم حارس المرمى الفائز بجائزة القفاز الذهبي في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>تيبو كورتوا</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كورتوا / تيبو كورتوا / Thibaut Courtois</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الكولومبي الفائز بالحذاء الذهبي في كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>خاميس رودريغيز</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: خاميس رودريجيز / جيمس رودريغيز / رودريغيز / James Rodríguez. سجل 6 أهداف</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الجائزة التي تُمنح للمنتخب الأكثر التزاماً بالروح الرياضية في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>جائزة اللعب النظيف</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: اللعب النظيف / FIFA Fair Play Award</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مدرب المنتخب الفائز بكأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>فيسنتي ديل بوسكي</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ديل بوسكي / فيسينتي ديل بوسكي / Vicente del Bosque</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم قائد ألمانيا الغربية الذي رفع كأس العالم 1974م لاعباً وفاز بها مدرباً عام 1990م؟</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>فرانتس بيكنباور</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بيكنباور / بكنباور / فرانز بيكنباور / Franz Beckenbauer</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم منتخب الدولة الأوروبية الأصغر سكاناً بين المنتخبات المشاركة في نهائيات كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>آيسلندا</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أيسلندا / ايسلندا / منتخب آيسلندا. شاركت في نسخة 2018م</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي حلّ ثالثاً في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>بلجيكا</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب بلجيكا / الشياطين الحمر. فاز على إنجلترا 2-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم منتخب أمريكا الوسطى الذي تصدّر مجموعته القوية وبلغ ربع نهائي كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>كوستاريكا</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كوستاريكا / منتخب كوستاريكا. ضمت مجموعته أوروغواي وإيطاليا وإنجلترا</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب رومانيا الملقب بـ(مارادونا الكاربات)، نجم كأس العالم 1994م؟</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>جورجي هاجي</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: هاجي / جيورجي هاجي / غيورغي هاجي / Gheorghe Hagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الحكم الشهير بصلعه الذي أدار المباراة النهائية لكأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>بييرلويجي كولينا</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كولينا / بيير لويجي كولينا / Pierluigi Collina</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مهاجم فرنسا الفائز بجائزة الكرة الذهبية لمجلة فرانس فوتبول (البالون دور) لعام 2022م الذي غاب عن كأس العالم في قطر بسبب الإصابة؟</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>كريم بنزيما</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بنزيما / بنزيمة / Karim Benzema. لا يُقبل: مبابي</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>كم مرة فازت إيطاليا بكأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>4 مرات</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أربع مرات / 4. الأعوام: 1934 و1938 و1982 و2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي هزم قطر 2-0 في المباراة الافتتاحية لكأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>الإكوادور</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الاكوادور / منتخب الإكوادور</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم المجر الملقب بـ(الرائد الراكض)، قائد المجر في نهائي كأس العالم 1954م؟</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>فيرينك بوشكاش</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بوشكاش / فيرنس بوشكاش / Ferenc Puskás</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب العربي الثالث الذي شارك في مونديال المكسيك 1986م إلى جانب منتخبين مغاربيين؟</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب العراق / أسود الرافدين</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي هزم الولايات المتحدة 2-1 في كأس العالم 1998م؟</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>إيران</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إيران / تيم ملي</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم حارس المرمى الملقب بـ(العنكبوت الأسود) والذي حملت جائزة أفضل حارس في كأس العالم اسمه بين عامي 1994 و2006م؟</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ليف ياشين</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ياشين / Lev Yashin. سُميت الجائزة باسمه من 1994 إلى 2006 ثم صارت القفاز الذهبي منذ 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>كم مباراة تُقام في كأس العالم بنظام الـ32 منتخباً؟</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 64 مباراة / أربع وستون</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الملقب بـ(النسور الممتازة)؟</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>نيجيريا</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب نيجيريا / Super Eagles</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>في أي مدينة يقع المقر الرئيسي للفيفا؟</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>زيورخ</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: زيوريخ / Zurich</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>كم نسخة أُقيمت من كأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 22 نسخة / اثنتان وعشرون</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>كم منتخباً فاز بكأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 8 منتخبات / ثمانية</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم أوكرانيا الذي قاد منتخب بلاده إلى ربع نهائي كأس العالم 2006م في مشاركته الأولى؟</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>أندريه شيفتشينكو</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: شيفتشينكو / شيفشنكو / Andriy Shevchenko</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم القارة (باستثناء القطب الجنوبي) الوحيدة التي لم تستضف كأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>أوقيانوسيا</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أوقيانيا / أستراليا وأوقيانوسيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مدرب إيطاليا الذي قاد منتخب بلاده للقب كأس العالم 2006م؟</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>مارتشيلو ليبي</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ليبي / مارشيلو ليبي / Marcello Lippi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة الكاريبية التي أصبحت أصغر دولة سكاناً تتأهل إلى كأس العالم للرجال في نسخة 2026م؟</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>كوراساو</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كوراكاو / Curaçao. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي حقق فوزاً تاريخياً بنتيجة 1-0 على جاره الغربي صاحب الأرض في كأس العالم، وكانت مشاركته الوحيدة؟</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ألمانيا الشرقية</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ألمانيا الديمقراطية / منتخب ألمانيا الشرقية</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الشائع لأربعة منتخبات صعدت إلى دور الـ16 من غير المركزين الأول والثاني في مجموعاتها بنظام الـ24 منتخباً؟</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>أفضل الثوالث</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أفضل أصحاب المركز الثالث / أفضل المنتخبات الثالثة. طُبق هذا النظام بين 1986 و1994م</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدرب البرازيلي الذي قاد منتخبات الكويت والإمارات والسعودية في كأس العالم، وفاز باللقب مع البرازيل 1994م؟</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>كارلوس ألبرتو باريرا</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: باريرا / كارلوس ألبرتو باريرا / Parreira. قاد الكويت 1982 والإمارات 1990 والبرازيل 1994 و2006 والسعودية 1998 وجنوب أفريقيا 2010. بورا ميلوتينوفيتش يتقاسم معه رقم خمسة منتخبات، لكن السؤال عن المدرب البرازيلي</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي حلّ ثالثاً في كأس العالم 1982م وكان نجمه زبيغنيو بونيك؟</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>بولندا</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب بولندا</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي شارك في سبع نسخ من كأس العالم بين عامي 1958 و1990م قبل أن تنقسم دولته؟</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>الاتحاد السوفيتي</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الاتحاد السوفييتي / منتخب الاتحاد السوفيتي / الاتحاد السوفياتي</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب تركيا الذي سجل أسرع هدف في تاريخ كأس العالم بعد 11 ثانية حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>هاكان شوكور</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: شوكور / هاكان سوكور / Hakan Şükür. سجله في مباراة المركز الثالث عام 2002م</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الكاريبي الذي شارك في كأس العالم 1998م للمرة الوحيدة في تاريخه حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>جامايكا</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب جامايكا / ريغي بويز</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>ما نتيجة نهائي كأس العالم 1998م؟</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 0-3 / ثلاثة مقابل صفر</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>في أي دولة أُقيمت نهائيات كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>البرازيل</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة الثالثة التي ستستضيف مباراة افتتاحية في كأس العالم 2030م إلى جانب الأوروغواي والأرجنتين احتفالاً بمئوية البطولة؟</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>باراغواي</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: باراجواي / بارجواي. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>في أي عاصمة أوروبية تأسس الاتحاد الدولي لكرة القدم؟</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>باريس</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم ريال مدريد التاريخي الذي مثّل ثلاثة منتخبات ولم يشارك قط في نهائيات كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>ألفريدو دي ستيفانو</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: دي ستيفانو / ألفريدو دي ستيفانو / Alfredo Di Stéfano. مثّل الأرجنتين وكولومبيا وإسبانيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدرب الهولندي الذي قاد منتخباً آسيوياً مضيفاً إلى نصف نهائي كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>غوس هيدينك</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: هيدينك / هيدنك / Guus Hiddink</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>كم دولة من قارة أمريكا الجنوبية فازت بكأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>ثلاث دول</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ثلاث دول / ثلاثة. الدول: الأوروغواي والبرازيل والأرجنتين</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي فاز بكأس العالم للسيدات عام 2011م على الولايات المتحدة بركلات الترجيح؟</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>اليابان</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب اليابان. انتهت المباراة 2-2 وفازت اليابان 3-1 بركلات الترجيح</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول دولة تستضيف كأس العالم للرجال للمرة الثالثة في نسخة 2026م؟</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>المكسيك</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مكسيك. سبق أن استضافت 1970 و1986. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة الأكثر سكاناً في العالم التي لم يشارك منتخبها في نهائيات كأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>الهند</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: India. تأهلت عام 1950م لكنها انسحبت</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم المغرب الذي توّج بجائزة أفضل لاعب في أفريقيا عام 1998م وسجّل في مونديال ذلك العام؟</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>مصطفى حجي</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: حجي / Mustapha Hadji</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم السنغال الذي غاب عن مونديال قطر بسبب إصابة قبل انطلاق البطولة؟</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>ساديو ماني</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ماني / Sadio Mané</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم قائد كوريا الجنوبية الذي لعب بقناع واقٍ على وجهه في مونديال قطر؟</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>سون هيونغ مين</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: سون / سون هيونج مين / Son Heung-min</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي خسر 5-1 أمام هولندا و2-0 أمام تشيلي وودّع كأس العالم 2014م من الدور الأول؟</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>إسبانيا</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إسبانيا / أسبانيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي هزم ألمانيا وإسبانيا في دور المجموعات بكأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>اليابان</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب اليابان. فاز على كل منهما 2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي أُطلق على الحرب القصيرة بين السلفادور وهندوراس عام 1969م التي ارتبطت بمباريات التصفيات المؤهلة لكأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>حرب كرة القدم</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: حرب الكرة / حرب المئة ساعة / Football War</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي عُرف به فوز ألمانيا الغربية بنهائي كأس العالم 1954م رغم أنها لم تكن المرشح الأبرز؟</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>معجزة برن</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: معجزة بيرن / معجزة برن / Miracle of Bern</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم حارس المرمى الوحيد الذي فاز بجائزة الكرة الذهبية لأفضل لاعب في كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>أوليفر كان</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كان / أوليفر خان / Oliver Kahn. فاز بها عام 2002م</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول منتخب من قارة أوقيانوسيا يتأهل إلى نهائيات كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>أستراليا</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب أستراليا. تأهلت عام 1974م</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الذي شارك لأول مرة في كأس العالم بقيادة المهاجم إيمانويل أديبايور؟</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>توغو</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب توغو. شارك عام 2006م ومشاركته الوحيدة حتى نسخة 2022م</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول منتخب أفريقي يتجاوز دور المجموعات في نهائيات كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب المغرب. حدث ذلك عام 1986م</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي فاز بالمركز الثالث في كأس العالم 2014م على حساب صاحب الأرض؟</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>هولندا</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب هولندا / الطواحين. فاز 3-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب المتوّج بكأس العالم سابقاً الذي غاب عن ثلاث نسخ متتالية (2018 و2022 و2026م)؟</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>إيطاليا</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إيطاليا / ايطاليا. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي توّج بطلاً لكأس العالم 1978م على أرضه؟</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>الأرجنتين</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الأرجنتين</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأكثر مشاركة في كأس العالم دون أن يفوز بها حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>المكسيك</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب المكسيك. شارك 17 مرة</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب العربي الذي بلغ دور الـ16 في كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>الجزائر</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الجزائر</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الوحيد الذي بلغ دور الـ16 في كأس العالم 2006م؟</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>غانا</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب غانا</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أصغر لاعب سجل هدفاً في تاريخ كأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>بيليه</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بيلي / Pelé. كان عمره 17 عاماً وقت هدفه عام 1958م</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي شارك في كأس العالم 1998م لأول مرة في تاريخه؟</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>اليابان</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب اليابان</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الأكثر مشاركة في كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>الكاميرون</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الكاميرون. شارك ثماني مرات</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم النجم الذي عادل رقم بيليه كأفضل هداف في تاريخ منتخب بلاده بهدفه في ربع نهائي كأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>نيمار</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: نيمار جونيور / Neymar</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي يمثله جورج ويا الفائز بالكرة الذهبية الأوروبية عام 1995م دون أن يشارك قط في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>ليبيريا</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب ليبيريا</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدرب الذي قاد ألمانيا إلى لقب كأس العالم بعد انتظار دام 24 عاماً؟</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>يواخيم لوف</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: لوف / يوآخيم لوف / Joachim Löw</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم قائد البرازيل الذي ظهر في ثلاث نهائيات متتالية لكأس العالم ورفع الكأس في آخرها؟</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>كافو</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Cafu / ماركوس كافو</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي مثّله لاعب الوسط كيفين دي بروين في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>بلجيكا</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب بلجيكا</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي هزم البرتغال في دور المجموعات بكأس العالم 2022م وتأهل إلى ثمن النهائي؟</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>كوريا الجنوبية</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كوريا الجنوبية / كوريا. فاز 2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي أُطلق على مباراة دور المجموعات عام 1982م التي انتهت 1-0 بنتيجة اعتُبرت متفقاً عليها وأدت إلى إقامة مباريات الجولة الأخيرة في وقت واحد؟</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>عار خيخون</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فضيحة خيخون / مؤامرة خيخون / Disgrace of Gijón</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى كولومبيا بركلات الترجيح في ثمن نهائي كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>إنجلترا</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إنجلترا / انجلترا</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي اشتهرت جماهيره بتصفيق (الفايكنغ) وشارك في كأس العالم لأول مرة عام 2018م؟</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>آيسلندا</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أيسلندا / ايسلندا / منتخب آيسلندا</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي مثّله المهاجم زلاتان إبراهيموفيتش في كأس العالم 2006م؟</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>السويد</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب السويد</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم ألمانيا من أصول تركية الذي اعتزل اللعب الدولي بعد كأس العالم 2018م متهماً الاتحاد الألماني بالعنصرية؟</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>مسعود أوزيل</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أوزيل / مسعود اوزيل / Mesut Özil</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأمريكي الشمالي الوحيد الذي بلغ نصف نهائي كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>الولايات المتحدة</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أمريكا / الولايات المتحدة الأمريكية. حدث ذلك عام 1930م</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الأكثر تسجيلاً للأهداف في تاريخ كأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>ميروسلاف كلوزه</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كلوزه / ميروسلاف كلوسه / Miroslav Klose. لا يُقبل: ميسي (عادل الرقم في 2026م) / رونالدو البرازيلي (15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم البرازيل الذي سجل هدفاً من ركلة حرة بعيدة فوق حارس إنجلترا في ربع نهائي كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>رونالدينيو</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رونالدينهو / رونالدينيو غاوتشو / Ronaldinho</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب صاحب أكبر عدد من المشاركات في مباريات كأس العالم للرجال حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>ليونيل ميسي</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ميسي / Lionel Messi. لا يُقبل: لوثار ماتيوس (25، الرقم السابق)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم كولومبيا ذي الشعر الأشقر المجعد الذي شارك في ثلاث نسخ متتالية من كأس العالم بدءاً من 1990م؟</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>كارلوس فالديراما</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فالديراما / كارلوس فالديراما / Carlos Valderrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب غير الأوروبي الوحيد الذي فاز بكأس العالم على أرض أوروبية حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>البرازيل</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب البرازيل. فاز عام 1958م في السويد</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب المضيف الذي أقصته الأرجنتين بركلات الترجيح من نصف نهائي كأس العالم 1990م؟</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>إيطاليا</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إيطاليا / ايطاليا</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مدافع كولومبيا الذي سجل هدفاً عكسياً في كأس العالم 1994م وقُتل في بلاده بعد أيام من خروج منتخبه؟</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>أندريس إسكوبار</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: إسكوبار / اندريس اسكوبار / Andrés Escobar. لا يُقبل: بابلو إسكوبار</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى المضيف ألمانيا من نصف نهائي كأس العالم 2006م؟</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>إيطاليا</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إيطاليا / ايطاليا</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى البرازيل من ربع نهائي كأس العالم 2010م بنتيجة 2-1؟</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>هولندا</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب هولندا</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى هولندا بركلات الترجيح من نصف نهائي كأس العالم 1998م؟</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>البرازيل</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب البرازيل</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي قاطع لاعبوه التدريب بعد استبعاد زميلهم نيكولا أنيلكا في كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>فرنسا</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب فرنسا</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم هولندا الذي سجل هدف الفوز في الدقيقة 90 أمام الأرجنتين في ربع نهائي كأس العالم 1998م؟</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>دينيس بيركامب</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بيركامب / بركامب / Dennis Bergkamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي هزم الأرجنتين 4-0 في ربع نهائي كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>ألمانيا</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D185" s="2" t="inlineStr"/>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب ألمانيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم فرنسا الذي أضاع ركلة ترجيح في ربع نهائي كأس العالم 1986م رغم فوز منتخبه؟</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>ميشيل بلاتيني</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D186" s="2" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بلاتيني / Michel Platini</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب البديل الذي سجل هدف الفوز في الدقيقة 113 من نهائي كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>ماريو غوتزه</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D187" s="2" t="inlineStr"/>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: غوتزه / غوتسه / Mario Götze</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الشقيقين اللذين مثّلا ألمانيا وغانا ولعبا ضد بعضهما في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>بواتينغ</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D188" s="2" t="inlineStr"/>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الأخوان بواتينغ / جيروم وكيفن برنس بواتينغ / Boateng</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأمريكي الجنوبي الذي أقصى الأوروغواي من ثمن نهائي كأس العالم 2014م بهدفين دون رد؟</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>كولومبيا</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D189" s="2" t="inlineStr"/>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كولومبيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب البلقاني الذي شارك لأول مرة في كأس العالم بقيادة نجمه إدين جيكو؟</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>البوسنة والهرسك</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D190" s="2" t="inlineStr"/>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: البوسنة / Bosnia and Herzegovina. شارك عام 2014م</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب فرنسا الذي لمس الكرة بيده قبل تمريرة هدف التأهل أمام أيرلندا في ملحق التصفيات المؤهلة لكأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>تييري هنري</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D191" s="2" t="inlineStr"/>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: هنري / Thierry Henry</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم الأرجنتين الذي طُرد من كأس العالم 1994م بعد ثبوت تعاطيه مادة محظورة؟</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>دييغو مارادونا</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D192" s="2" t="inlineStr"/>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مارادونا / Diego Maradona</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الاستاد الذي أُقيمت عليه المباراة النهائية لكأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>استاد لوسيل</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D193" s="2" t="inlineStr"/>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ملعب لوسيل / لوسيل / Lusail Stadium</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول أغنية أصدرها الفيفا ضمن الألبوم الرسمي لكأس العالم 2022م، وشارك في أدائها ديفيدو وعائشة وترينيداد كاردونا؟</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>هيا هيا</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D194" s="2" t="inlineStr"/>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: هيّا هيّا / Hayya Hayya / أفضل معاً</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب العربي الوحيد الذي شارك في كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>الجزائر</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D195" s="2" t="inlineStr"/>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الجزائر / محاربو الصحراء</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي أُطلق على هدف مارادونا الثاني في ربع نهائي كأس العالم 1986م بعد أن راوغ عدداً من لاعبي الخصم؟</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>هدف القرن</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D196" s="2" t="inlineStr"/>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Goal of the Century</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول لاعب في تاريخ كأس العالم للرجال يسجل في خمس نسخ مختلفة حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>كريستيانو رونالدو</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D197" s="2" t="inlineStr"/>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رونالدو / Cristiano Ronaldo. لا يُقبل: ميسي</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى ألمانيا في ربع نهائي كأس العالم 1994م وبلغ نصف النهائي لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>بلغاريا</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D198" s="2" t="inlineStr"/>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب بلغاريا. فاز 2-1 وكان نجمه هريستو ستويتشكوف</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب فرنسا صاحب الرقم القياسي بتسجيل 13 هدفاً في نسخة واحدة من كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>جوست فونتين</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D199" s="2" t="inlineStr"/>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: جاست فونتين / فونتين / Just Fontaine. حدث ذلك في نسخة 1958م</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم حُسمت مباراة بركلات الترجيح لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D200" s="2" t="inlineStr"/>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1982م / إسبانيا 1982. كانت في نصف النهائي بين ألمانيا الغربية وفرنسا</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الكرة الرسمية لدور المجموعات في كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>تيلستار 18</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D201" s="2" t="inlineStr"/>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: تلستار 18 / تيلستار / Telstar 18. الكرة الرسمية لأدوار خروج المغلوب كانت «تيلستار ميشتا» وليست الإجابة</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الحكم الإنجليزي الذي أدار المباراة النهائية لكأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>هوارد ويب</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D202" s="2" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ويب / Howard Webb</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب ألمانيا الغربية الذي سجل هدف الفوز 3-2 في نهائي كأس العالم 1954م؟</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>هيلموت ران</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D203" s="2" t="inlineStr"/>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ران / هلموت ران / Helmut Rahn</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدرب الوحيد الذي فاز بلقبين في كأس العالم كمدرب حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>فيتوريو بوتزو</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D204" s="2" t="inlineStr"/>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بوتزو / بوتسو / فيتوريو بوزو / Vittorio Pozzo. فاز بنسختي 1934 و1938</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الوحيد الذي سجّل 10 أهداف في مباراة واحدة بكأس العالم حتى نسخة 2022م، وذلك أمام السلفادور عام 1982م؟</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>المجر</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D205" s="2" t="inlineStr"/>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: هنغاريا / منتخب المجر. أكبر فارق (9) يتقاسمه معه مباراتا المجر–كوريا الجنوبية 1954 ويوغوسلافيا–زائير 1974</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي شهدت نسختها عام 1954م أعلى معدل أهداف لكل مباراة في تاريخ كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>سويسرا</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D206" s="2" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>المعدل 5.38 هدف للمباراة (140 هدفاً في 26 مباراة)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>كم منتخباً شارك في أول نسخة من كأس العالم عام 1930م؟</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D207" s="2" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 13 منتخباً / ثلاثة عشر</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب فرنسا الذي سجل أول هدف ذهبي في تاريخ كأس العالم أمام باراغواي عام 1998م؟</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>لوران بلان</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D208" s="2" t="inlineStr"/>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بلان / Laurent Blanc</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أصبح أول من يحتفظ بلقب كأس العالم بعد فوزه به عام 1934م؟</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>إيطاليا</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D209" s="2" t="inlineStr"/>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب إيطاليا / الأزوري. فاز باللقب في 1934 و1938</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل ثلاثية في نهائي كأس العالم 1966م؟</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>جيف هيرست</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D210" s="2" t="inlineStr"/>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: هيرست / جيوف هيرست / Geoff Hurst</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي عُرفت به مباراة تشيلي وإيطاليا في كأس العالم 1962م بسبب عنفها وطرد لاعبين فيها؟</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>معركة سانتياغو</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D211" s="2" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: معركة سانتياجو / Battle of Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي بلغ ربع نهائي كأس العالم 1966م في أول مشاركة له؟</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>كوريا الشمالية</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D212" s="2" t="inlineStr"/>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كوريا الشمالية</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي تأهل إلى كأس العالم بعد مباراة ملحق ضد إسرائيل لأن خصومها انسحبوا من التصفيات؟</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>ويلز</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D213" s="2" t="inlineStr"/>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب ويلز. رفضت تركيا وإندونيسيا والسودان ومصر مواجهة إسرائيل، فاشترط الفيفا خوضها مباراة، وكانت ويلز المنتخب الذي وقع عليه الاختيار</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم حارس مرمى المكسيك الملقب بـ(لا توتا)، وأول لاعب في التاريخ يشارك في خمس نسخ من كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>أنطونيو كاربخال</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D214" s="2" t="inlineStr"/>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كاربخال / كارباخال / Antonio Carbajal. شارك في نسخ 1950 إلى 1966</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الكاريبي الذي بلغ ربع نهائي كأس العالم 1938م؟</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>كوبا</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D215" s="2" t="inlineStr"/>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كوبا</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم ارتفع عدد المنتخبات المشاركة من 24 إلى 32؟</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D216" s="2" t="inlineStr"/>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1998م / فرنسا 1998</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم طُبّق نظام (ثلاث نقاط للفوز) لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D217" s="2" t="inlineStr"/>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1994م / أمريكا 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الاستاد الذي أُقيمت عليه المباراة النهائية لكأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>لوجنيكي</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D218" s="2" t="inlineStr"/>
+      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: استاد لوجنيكي / ملعب لوجنيكي / لوزنيكي / Luzhniki. يقع في موسكو</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المهاجم الذي سجل أربعة أهداف في مباراة واحدة من كأس العالم 1938م رغم خسارة منتخبه 5-6؟</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>إرنست فيلموفسكي</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D219" s="2" t="inlineStr"/>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فيلموفسكي / إرنست فيلموفسكي / Ernst Wilimowski / Ernest Wilimowski</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي يحمل الرقم القياسي بتسجيل خمسة أهداف في مباراة واحدة من كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>أوليغ سالينكو</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D220" s="2" t="inlineStr"/>
+      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: سالينكو / أولج سالينكو / Oleg Salenko. سجلها عام 1994م أمام الكاميرون</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>بأي نتيجة انتهت المباراة النهائية لكأس العالم 1930م؟</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D221" s="2" t="inlineStr"/>
+      <c r="E221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 2-4 / أربعة مقابل اثنين</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول تميمة رسمية في تاريخ كأس العالم، ظهرت عام 1966م؟</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>ويلي</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D222" s="2" t="inlineStr"/>
+      <c r="E222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ويلي / ويلي الأسد / World Cup Willie</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الكرة الرسمية لكأس العالم 1986م، وهي أول كرة اصطناعية بالكامل في تاريخ البطولة؟</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>أزتيكا</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D223" s="2" t="inlineStr"/>
+      <c r="E223" s="2" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أزتيك / Azteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة الآسيوية التي شاركت في كأس العالم 1938م باسم (جزر الهند الشرقية الهولندية)؟</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>إندونيسيا</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D224" s="2" t="inlineStr"/>
+      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: اندونيسيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أصبح عام 1974م أول منتخب من أفريقيا جنوب الصحراء يشارك في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>زائير</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D225" s="2" t="inlineStr"/>
+      <c r="E225" s="2" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب زائير / الكونغو الديمقراطية</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي خسر نهائي كأس العالم عامي 1934 و1962م؟</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>تشيكوسلوفاكيا</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D226" s="2" t="inlineStr"/>
+      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب تشيكوسلوفاكيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم استُخدمت البطاقتان الصفراء والحمراء لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D227" s="2" t="inlineStr"/>
+      <c r="E227" s="2" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1970م / المكسيك 1970</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب البريطاني الذي شارك في ثماني نسخ ولم يتجاوز دور المجموعات أبداً حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>اسكتلندا</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D228" s="2" t="inlineStr"/>
+      <c r="E228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب اسكتلندا / سكوتلندا</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي استضافت أول نسخة من كأس العالم للسيدات عام 1991م؟</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>الصين</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D229" s="2" t="inlineStr"/>
+      <c r="E229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الصين الشعبية. أُقيمت في إقليم قوانغدونغ</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الوحيد الذي بلغ نصف نهائي أول نسخة عام 1930م؟</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>يوغوسلافيا</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D230" s="2" t="inlineStr"/>
+      <c r="E230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب يوغوسلافيا. بقية المنتخبات الأربعة: الأرجنتين والأوروغواي والولايات المتحدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم قائد الأوروغواي الذي رفع الكأس عام 1950م؟</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>أوبدوليو فاريلا</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D231" s="2" t="inlineStr"/>
+      <c r="E231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فاريلا / أوبديليو فاريلا / Obdulio Varela</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول شخص في التاريخ يفوز بكأس العالم لاعباً ثم مدرباً؟</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>ماريو زاغالو</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D232" s="2" t="inlineStr"/>
+      <c r="E232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: زاغالو / ماريو زاجالو / Mário Zagallo. فاز لاعباً عامي 1958 و1962 ومدرباً عام 1970. بيكنباور فاز لاعباً (1974) ومدرباً (1990) لكنه ليس الأول؛ الإجابة الصحيحة زاغالو</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الحكم الإنجليزي الذي ابتكر فكرة البطاقتين الصفراء والحمراء بعد أن استوحاها من إشارات المرور؟</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>كين أستون</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D233" s="2" t="inlineStr"/>
+      <c r="E233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كين آستون / Ken Aston</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم تأهلت المنتخبات الأربعة للمملكة المتحدة معاً، وهو ما لم يتكرر حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D234" s="2" t="inlineStr"/>
+      <c r="E234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1958م / السويد 1958</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل هدفاً شهيراً بعد مراوغة ثلاثة مدافعين هولنديين في كأس العالم 1978م؟</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>آرتشي جيميل</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D235" s="2" t="inlineStr"/>
+      <c r="E235" s="2" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: جيميل / جيمل / Archie Gemmill. فازت اسكتلندا 3-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم حارس مرمى أيرلندا الذي تصدى لركلة ترجيح رومانية قادت أيرلندا إلى ربع نهائي كأس العالم 1990م؟</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>باكي بونر</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D236" s="2" t="inlineStr"/>
+      <c r="E236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بونر / باكي بونير / Packie Bonner</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب الأوروغواي الذي نال أسرع بطاقة حمراء في تاريخ كأس العالم بعد 56 ثانية فقط حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>خوسيه باتيستا</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D237" s="2" t="inlineStr"/>
+      <c r="E237" s="2" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: باتيستا / Jose Batista. حدث ذلك عام 1986م أمام اسكتلندا</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أول لاعب أفريقي وعربي سجل هدفاً في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>عبدالرحمن فوزي</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D238" s="2" t="inlineStr"/>
+      <c r="E238" s="2" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: عبد الرحمن فوزي / فوزي / Abdelrahman Fawzi. سجل هدفين عام 1934م</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم رئيس الفيفا الذي بقي في منصبه 24 عاماً قبل أن يخلفه سيب بلاتر؟</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>جواو هافيلانج</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D239" s="2" t="inlineStr"/>
+      <c r="E239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: هافيلانج / هافلانج / جواو هافلانج / João Havelange</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم النحات الذي صمّم كأس العالم الحالية المستخدمة منذ سبعينيات القرن الماضي؟</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>سيلفيو غاتسانيغا</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D240" s="2" t="inlineStr"/>
+      <c r="E240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: غاتسانيغا / سيلفيو غازانيغا / غازانيغا / Silvio Gazzaniga</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي لُقّب بـ(واندرتيم) أي فريق المعجزة في ثلاثينيات القرن الماضي، وحلّ رابعاً في كأس العالم 1934م؟</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>النمسا</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D241" s="2" t="inlineStr"/>
+      <c r="E241" s="2" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب النمسا / Wunderteam</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم هداف نسخة 1934م الذي سجل خمسة أهداف؟</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>أولدريتش نيجيدلي</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D242" s="2" t="inlineStr"/>
+      <c r="E242" s="2" t="inlineStr"/>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: نيجيدلي / نيديلي / أولدريخ نيجدلي / Oldřich Nejedlý. اعترف الفيفا به هدافاً عام 2006م</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم بيرو الذي سجل عشرة أهداف في نسختي 1970 و1978م؟</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>تيوفيلو كوبيياس</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D243" s="2" t="inlineStr"/>
+      <c r="E243" s="2" t="inlineStr"/>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كوبيياس / كوبياس / Teófilo Cubillas. سجل خمسة في كل نسخة</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب البديل الذي سجل ثلاثة أهداف خلال سبع دقائق فقط في كأس العالم، وهي أسرع سلسلة أهداف في البطولة حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>لاسلو كيش</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D244" s="2" t="inlineStr"/>
+      <c r="E244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كيش / لازلو كيس / كيس / László Kiss. سجله عام 1982م وهو الوحيد الذي سجل هاتريك كبديل</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الحكم الأول من أفريقيا والوطن العربي الذي أدار نهائي كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>سعيد بلقولة</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D245" s="2" t="inlineStr"/>
+      <c r="E245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بلقولة / سعيد بلقولة المغربي / Said Belqola. أدار نهائي 1998م</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>كم هدفاً سُجّل في أكثر مباراة تسجيلاً للأهداف في تاريخ كأس العالم حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D246" s="2" t="inlineStr"/>
+      <c r="E246" s="2" t="inlineStr"/>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 12 هدفاً / اثنا عشر. انتهت 7-5 لصالح النمسا على سويسرا عام 1954م</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعبة المنتخب الأمريكي للسيدات الفائزة بالكرة الذهبية والحذاء الذهبي معاً في كأس العالم للسيدات 2019م؟</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>ميغان رابينو</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D247" s="2" t="inlineStr"/>
+      <c r="E247" s="2" t="inlineStr"/>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رابينو / ميجان رابينو / Megan Rapinoe. سجلت 6 أهداف</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي هزم الأوروغواي 6-1 في كأس العالم 1986م بثلاثية من نجمه بريبن إلكيير؟</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>الدنمارك</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D248" s="2" t="inlineStr"/>
+      <c r="E248" s="2" t="inlineStr"/>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الدنمارك. اشتهر حينها بلقب «الديناميت الدنماركي»</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أصغر لاعب شارك في مباراة بنهائيات كأس العالم، وكان يمثل أيرلندا الشمالية عام 1982م، حتى نسخة 2022م؟</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>نورمان وايتسايد</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D249" s="2" t="inlineStr"/>
+      <c r="E249" s="2" t="inlineStr"/>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: وايتسايد / ويتسايد / Norman Whiteside. كان عمره 17 عاماً و41 يوماً</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الأسلوب الذي حُسم به ترتيب منتخبين متعادلين في كل المعايير داخل إحدى مجموعات كأس العالم 1990م؟</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>القرعة</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D250" s="2" t="inlineStr"/>
+      <c r="E250" s="2" t="inlineStr"/>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: سحب القرعة / القرعة العشوائية. كانا أيرلندا وهولندا في المجموعة السادسة</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم نُقلت المباريات تلفزيونياً لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>1954</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D251" s="2" t="inlineStr"/>
+      <c r="E251" s="2" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1954م</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم استُخدمت تقنية خط المرمى لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D252" s="2" t="inlineStr"/>
+      <c r="E252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 2014م</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي سجل في كأس العالم 1974م هدفاً أنهى سلسلة تاريخية من أكثر من 1100 دقيقة دون استقبال أهداف لحارس مرمى أسطوري؟</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>هايتي</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D253" s="2" t="inlineStr"/>
+      <c r="E253" s="2" t="inlineStr"/>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب هايتي. سجله إيمانويل سانون وكانت السلسلة 1142 دقيقة</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الملك الذي اختار بنفسه لاعبي منتخب بلاده وحصل لهم على إجازة من أعمالهم للمشاركة في كأس العالم 1930م؟</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>كارول الثاني</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D254" s="2" t="inlineStr"/>
+      <c r="E254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الملك كارول / كارول الثاني ملك رومانيا / Carol II</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل هدفاً مباشراً من ركلة ركنية في مباراة انتهت 4-4 في كأس العالم 1962م؟</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>ماركوس كول</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D255" s="2" t="inlineStr"/>
+      <c r="E255" s="2" t="inlineStr"/>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كول / ماركوس كول / Marcos Coll. وهو الهدف الأولمبي الوحيد في تاريخ البطولة حتى نسخة 2022م</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدافع الذي ركض وركل الكرة بعيداً قبل تنفيذ خصمه ركلة حرة في إحدى مباريات كأس العالم في واقعة طريفة؟</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>مويبو إيلونغا</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D256" s="2" t="inlineStr"/>
+      <c r="E256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: إيلونغا / مويبو إيلونجا / Mwepu Ilunga. حدثت عام 1974م</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدرب الذي قاد منتخباً أفريقياً إلى ربع نهائي كأس العالم في أول مشاركة له؟</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>برونو ميتسو</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D257" s="2" t="inlineStr"/>
+      <c r="E257" s="2" t="inlineStr"/>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ميتسو / بروينو ميتسو / Bruno Metsu. تحقق ذلك عام 2002م مع السنغال</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم أكبر لاعب سناً يرفع كأس العالم حتى نسخة 2022م، وهو حارس مرمى فاز بها وعمره 40 عاماً؟</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>دينو زوف</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D258" s="2" t="inlineStr"/>
+      <c r="E258" s="2" t="inlineStr"/>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: زوف / دينو تسوف / Dino Zoff. فاز بها عام 1982م</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي أُطلق على مباراة نصف نهائي كأس العالم 1970م التي انتهت 4-3 بعد وقت إضافي؟</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>مباراة القرن</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D259" s="2" t="inlineStr"/>
+      <c r="E259" s="2" t="inlineStr"/>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مباراة القرن / Game of the Century</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدافع الهولندي الذي سجل هدفاً في مرماه ثم هدفاً في مرمى الخصم في المباراة نفسها بكأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>إيرني براندتس</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D260" s="2" t="inlineStr"/>
+      <c r="E260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: براندتس / إيرني براندس / Ernie Brandts. حدث ذلك عام 1978م في فوز هولندا 2-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>في أي مدينة إسبانية عُقد مؤتمر الفيفا عام 1929م الذي اختار الدولة المضيفة لأول نسخة؟</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>برشلونة</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D261" s="2" t="inlineStr"/>
+      <c r="E261" s="2" t="inlineStr"/>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Barcelona</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الحكم البلجيكي الذي أدار نهائي أول نسخة من كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>جون لانغينوس</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D262" s="2" t="inlineStr"/>
+      <c r="E262" s="2" t="inlineStr"/>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: لانغينوس / جون لانجينوس / John Langenus. أُقيمت عام 1930م</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الذي خسر أمام فرنسا في دور الـ16 بكأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>نيجيريا</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D263" s="2" t="inlineStr"/>
+      <c r="E263" s="2" t="inlineStr"/>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب نيجيريا / النسور الممتازة</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي يضع أربع نجوم على قميصه رغم فوزه بكأس العالم مرتين فقط؟</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>الأوروغواي</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D264" s="2" t="inlineStr"/>
+      <c r="E264" s="2" t="inlineStr"/>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أوروغواي / أوروجواي. تشمل النجوم لقبين أولمبيين (1924 و1928)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي كانت مقررة لاستضافة كأس العالم قبل أن تعتذر لأسباب مالية وحلّت المكسيك بدلاً منها؟</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>كولومبيا</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D265" s="2" t="inlineStr"/>
+      <c r="E265" s="2" t="inlineStr"/>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كولومبيا. حلّت المكسيك بدلاً منها عام 1983م</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم منتخب الكونكاكاف الذي بلغ ربع نهائي كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>الولايات المتحدة</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D266" s="2" t="inlineStr"/>
+      <c r="E266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أمريكا / الولايات المتحدة الأمريكية</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي حلّ رابعاً في كأس العالم 1938م؟</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>السويد</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D267" s="2" t="inlineStr"/>
+      <c r="E267" s="2" t="inlineStr"/>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب السويد. خسر مباراة المركز الثالث 2-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي قاطع كأس العالم 1934م رغم أنه حامل اللقب؟</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>الأوروغواي</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D268" s="2" t="inlineStr"/>
+      <c r="E268" s="2" t="inlineStr"/>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أوروغواي / أوروجواي</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي حلّ رابعاً في كأس العالم 1986م بعد خسارته نصف النهائي 0-2؟</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>بلجيكا</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D269" s="2" t="inlineStr"/>
+      <c r="E269" s="2" t="inlineStr"/>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب بلجيكا</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الذي خرج من دور المجموعات في كأس العالم 1982م دون أن يخسر أي مباراة؟</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>الكاميرون</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D270" s="2" t="inlineStr"/>
+      <c r="E270" s="2" t="inlineStr"/>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الكاميرون. تعادل في مبارياته الثلاث</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مدرب الأوروغواي الذي فاز بكأس العالم 1950م؟</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>خوان لوبيز</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D271" s="2" t="inlineStr"/>
+      <c r="E271" s="2" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: لوبيز / خوان لوبيز فونتانا / Juan López</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مدرب إيطاليا الذي قادها للقب كأس العالم بعد 44 عاماً من لقبها السابق؟</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>إنزو بيرزوت</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D272" s="2" t="inlineStr"/>
+      <c r="E272" s="2" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بيرزوت / إنتسو بيرتسوت / Enzo Bearzot</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مدرب المجر الذي قاد الفريق الذهبي إلى المباراة النهائية لكأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>غوستاف سيبيش</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D273" s="2" t="inlineStr"/>
+      <c r="E273" s="2" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: سيبيش / غوستاف سيبيس / Gusztáv Sebes. حدث ذلك عام 1954م</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي استقبل 16 هدفاً في مباراتين فقط خلال نسخة 1954م؟</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>كوريا الجنوبية</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D274" s="2" t="inlineStr"/>
+      <c r="E274" s="2" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كوريا الجنوبية / كوريا. خسر 0-9 و0-7. رقم قياسي حتى نسخة 2022م</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي خرج من كأس العالم 2006م بركلات الترجيح دون أن يستقبل أي هدف طوال البطولة؟</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>سويسرا</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D275" s="2" t="inlineStr"/>
+      <c r="E275" s="2" t="inlineStr"/>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب سويسرا. خسر 0-3 بركلات الترجيح</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المعيار الذي استُخدم لأول مرة في كأس العالم 1970م لترتيب المنتخبات المتساوية في النقاط؟</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>فارق الأهداف</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D276" s="2" t="inlineStr"/>
+      <c r="E276" s="2" t="inlineStr"/>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الفارق التهديفي / Goal difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>ما نتيجة المباراة النهائية لكأس العالم 1958م؟</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D277" s="2" t="inlineStr"/>
+      <c r="E277" s="2" t="inlineStr"/>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 2-5 / خمسة مقابل اثنين</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم السفينة الإيطالية التي حملت عدة منتخبات وكأس البطولة لحضور النسخة الأولى من كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>كونتي فيردي</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D278" s="2" t="inlineStr"/>
+      <c r="E278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Conte Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي هزم البرازيل 2-1 في دور المجموعات بكأس العالم 1998م وتأهل على حساب المغرب؟</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>النرويج</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D279" s="2" t="inlineStr"/>
+      <c r="E279" s="2" t="inlineStr"/>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب النرويج</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم عاد الإقصاء المباشر بعد الدور الأول بدلاً من الدوري في المرحلة الثانية؟</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D280" s="2" t="inlineStr"/>
+      <c r="E280" s="2" t="inlineStr"/>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1986م / المكسيك 1986</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي انسحب من كأس العالم 1938م بعد ضم بلاده إلى ألمانيا؟</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>النمسا</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D281" s="2" t="inlineStr"/>
+      <c r="E281" s="2" t="inlineStr"/>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب النمسا</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل أول ركلة جزاء مُنحت بعد مراجعة تقنية الفار في تاريخ كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>أنطوان غريزمان</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D282" s="2" t="inlineStr"/>
+      <c r="E282" s="2" t="inlineStr"/>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: غريزمان / غريزيمان / Antoine Griezmann</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي شارك في كأس العالم 1994م لأول مرة وخسر مبارياته الثلاث دون أن يسجل أي هدف؟</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>اليونان</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D283" s="2" t="inlineStr"/>
+      <c r="E283" s="2" t="inlineStr"/>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب اليونان</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المهاجم البرتغالي الذي سجل ثلاثية في ثمن نهائي كأس العالم 2022م وهو يحل مكان النجم الأول لمنتخبه في التشكيلة الأساسية؟</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>غونزالو راموس</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D284" s="2" t="inlineStr"/>
+      <c r="E284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: راموس / جونزالو راموس / Gonçalo Ramos. فازت البرتغال 6-1 على سويسرا</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي أُطلق على مباراة ثمن نهائي كأس العالم 2006م التي شهدت أربع بطاقات حمراء وستة عشر إنذاراً؟</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>معركة نورمبرغ</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D285" s="2" t="inlineStr"/>
+      <c r="E285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: معركة نورمبيرغ / معركة نورنبرغ / Battle of Nuremberg. كانت بين البرتغال وهولندا</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم منتخب أمريكا الوسطى الذي بلغ ثمن النهائي في مشاركته الأولى في كأس العالم 1990م؟</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>كوستاريكا</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D286" s="2" t="inlineStr"/>
+      <c r="E286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب كوستاريكا</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الوحيد حتى نسخة 2022م الذي خسر نهائي كأس العالم مع منتخب ثم فاز باللقب مع منتخب آخر؟</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>لويس مونتي</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D287" s="2" t="inlineStr"/>
+      <c r="E287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مونتي / Luis Monti. خسر مع الأرجنتين 1930م وفاز مع إيطاليا 1934م</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي فاز بكأس العالم 1958م مع البرازيل ثم لعب في نسخة 1962م مع إيطاليا؟</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>خوسيه ألتافيني</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D288" s="2" t="inlineStr"/>
+      <c r="E288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ألتافيني / جوزيه ألتافيني / José Altafini</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم شاركت إيران لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D289" s="2" t="inlineStr"/>
+      <c r="E289" s="2" t="inlineStr"/>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1978م / الأرجنتين 1978</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم عادت مصر للمشاركة للمرة الثانية بعد غياب طويل؟</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D290" s="2" t="inlineStr"/>
+      <c r="E290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1990م / إيطاليا 1990</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب إيطاليا الذي سجل هدف الفوز في الوقت الإضافي من نصف نهائي كأس العالم 1970م أمام ألمانيا الغربية؟</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>جياني ريفيرا</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D291" s="2" t="inlineStr"/>
+      <c r="E291" s="2" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ريفيرا / جاني ريفيرا / Gianni Rivera. فازت إيطاليا 4-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>في أي نسخة من كأس العالم بُثّت المباريات بالألوان لأول مرة؟</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D292" s="2" t="inlineStr"/>
+      <c r="E292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: 1970م / المكسيك 1970</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدافع الفرنسي الذي سجل هدفيه الدوليين الوحيدين في نصف نهائي كأس العالم 1998م أمام كرواتيا؟</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>ليليان تورام</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D293" s="2" t="inlineStr"/>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: تورام / ليليان ثورام / Lilian Thuram</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي خرج بركلات الترجيح من ثمن نهائي كأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>اليونان</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D294" s="2" t="inlineStr"/>
+      <c r="E294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب اليونان. فازت كوستاريكا 5-3 بركلات الترجيح</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الكاريبي الذي تعادل مع السويد 0-0 في كأس العالم 2006م؟</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>ترينيداد وتوباغو</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D295" s="2" t="inlineStr"/>
+      <c r="E295" s="2" t="inlineStr"/>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ترينيداد / Trinidad and Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>ما الاسم الذي أُطلق على مباراة الدور الثاني في كأس العالم 1982م التي سجل فيها باولو روسي ثلاثية وأقصى منتخباً ساحراً؟</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>مأساة سارية</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D296" s="2" t="inlineStr"/>
+      <c r="E296" s="2" t="inlineStr"/>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مأساة ساريا / مأساة سارياه / Sarrià Tragedy / Tragedy of Sarrià. كانت بين إيطاليا والبرازيل (3-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى السنغال بهدف ذهبي من ربع نهائي كأس العالم 2002م؟</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>تركيا</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D297" s="2" t="inlineStr"/>
+      <c r="E297" s="2" t="inlineStr"/>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب تركيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى اليابان بركلات الترجيح من ثمن نهائي كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>باراغواي</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D298" s="2" t="inlineStr"/>
+      <c r="E298" s="2" t="inlineStr"/>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب باراغواي / باراجواي</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي استضافت كأس العالم 1982م؟</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>إسبانيا</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D299" s="2" t="inlineStr"/>
+      <c r="E299" s="2" t="inlineStr"/>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أسبانيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأوروبي الذي خسر 0-1 أمام اليابان في أول فوز ياباني بكأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>روسيا</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D300" s="2" t="inlineStr"/>
+      <c r="E300" s="2" t="inlineStr"/>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب روسيا. حدث ذلك عام 2002م</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب قطر الذي سجل أول هدف لبلاده في تاريخ كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>محمد مونتاري</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D301" s="2" t="inlineStr"/>
+      <c r="E301" s="2" t="inlineStr"/>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مونتاري / Mohammed Muntari</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم منتخب أمريكا الوسطى الذي شارك في كأس العالم 2018م لأول مرة في تاريخه؟</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>بنما</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D302" s="2" t="inlineStr"/>
+      <c r="E302" s="2" t="inlineStr"/>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب بنما / Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي استضافت كأس العالم 1958م؟</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>السويد</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D303" s="2" t="inlineStr"/>
+      <c r="E303" s="2" t="inlineStr"/>
+      <c r="F303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الدولة التي استضافت كأس العالم 1938م؟</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>فرنسا</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D304" s="2" t="inlineStr"/>
+      <c r="E304" s="2" t="inlineStr"/>
+      <c r="F304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل هدف الفوز 3-2 في نهائي كأس العالم 1986م؟</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>خورخي بوروتشاغا</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D305" s="2" t="inlineStr"/>
+      <c r="E305" s="2" t="inlineStr"/>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بوروتشاغا / بوروتشاجا / Jorge Burruchaga</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المدافع الذي سجل ركلة الجزاء الحاسمة في نهائي كأس العالم 1990م؟</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>أندرياس برهمه</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D306" s="2" t="inlineStr"/>
+      <c r="E306" s="2" t="inlineStr"/>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: برهمه / بريمه / Andreas Brehme. سجلها في الدقيقة 85</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المهاجم الذي سجل أول هدف لمنتخب نيجيريا في تاريخ كأس العالم عام 1994م؟</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>رشيدي يكيني</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D307" s="2" t="inlineStr"/>
+      <c r="E307" s="2" t="inlineStr"/>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: يكيني / رشيد يكيني / Rashidi Yekini</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل ركلة جزاء في الدقيقة الثانية من نهائي كأس العالم 1974م؟</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>يوهان نيسكنس</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D308" s="2" t="inlineStr"/>
+      <c r="E308" s="2" t="inlineStr"/>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: نيسكنس / نيسكينز / Johan Neeskens</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل أول هدف في المباراة النهائية لأول نسخة من كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>بابلو دورادو</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D309" s="2" t="inlineStr"/>
+      <c r="E309" s="2" t="inlineStr"/>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: دورادو / Pablo Dorado. سجله في الدقيقة 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل هدف الفوز في الوقت الإضافي من نهائي كأس العالم 1934م؟</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>أنجيلو سكيافيو</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D310" s="2" t="inlineStr"/>
+      <c r="E310" s="2" t="inlineStr"/>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: سكيافيو / Angelo Schiavio</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مهاجم الأرجنتين الذي سجل هدف الفوز على البرازيل في ثمن نهائي كأس العالم 1990م؟</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>كلاوديو كانيجيا</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D311" s="2" t="inlineStr"/>
+      <c r="E311" s="2" t="inlineStr"/>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: كانيجيا / كانيغيا / Claudio Caniggia</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مهاجم البرازيل الذي احتفل بهدفه في كأس العالم 1994م بهزّ ذراعيه كأنه يهدهد طفلاً؟</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>بيبيتو</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D312" s="2" t="inlineStr"/>
+      <c r="E312" s="2" t="inlineStr"/>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Bebeto / بيبيتو</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم البرازيل الذي سجل في كل مباراة لبلاده في كأس العالم 1970م؟</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>جايرزينيو</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D313" s="2" t="inlineStr"/>
+      <c r="E313" s="2" t="inlineStr"/>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: جيرزينيو / جايرزينهو / Jairzinho</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب الكويت الذي سجل أول هدف لبلاده في تاريخ كأس العالم عام 1982م؟</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>فيصل الدخيل</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D314" s="2" t="inlineStr"/>
+      <c r="E314" s="2" t="inlineStr"/>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الدخيل / Faisal Al-Dakhil</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم وسط منتخب أيرلندا الذي غادر معسكر بلاده قبل كأس العالم 2002م بعد خلاف علني مع مدربه؟</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>روي كين</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D315" s="2" t="inlineStr"/>
+      <c r="E315" s="2" t="inlineStr"/>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Roy Keane. لا يُقبل: هاري كين</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الكلب الذي عثر على كأس العالم المسروقة في لندن عام 1966م؟</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>بيكلز</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D316" s="2" t="inlineStr"/>
+      <c r="E316" s="2" t="inlineStr"/>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: Pickles / بيكيلز</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم الأمير الكويتي الذي نزل إلى أرض الملعب احتجاجاً على هدف فرنسا في كأس العالم 1982م؟</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>الشيخ فهد الأحمد</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D317" s="2" t="inlineStr"/>
+      <c r="E317" s="2" t="inlineStr"/>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فهد الأحمد الصباح / فهد الأحمد الجابر الصباح / Sheikh Fahad Al-Ahmed. المصدران:</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الآسيوي الذي شارك في كأس العالم 2002م للمرة الأولى في تاريخه؟</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>الصين</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D318" s="2" t="inlineStr"/>
+      <c r="E318" s="2" t="inlineStr"/>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب الصين / الصين الشعبية</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب هولندا الذي طُرد في ثمن نهائي كأس العالم 1990م بعد أن بصق على لاعب ألماني؟</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>فرانك ريكارد</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D319" s="2" t="inlineStr"/>
+      <c r="E319" s="2" t="inlineStr"/>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ريكارد / ريكارت / Frank Rijkaard</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نجم البرازيل الذي قاد بلاده للقب كأس العالم 1962م بعد إصابة بيليه في المباراة الثانية؟</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>غارينشا</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D320" s="2" t="inlineStr"/>
+      <c r="E320" s="2" t="inlineStr"/>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: جارينشا / Garrincha</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي خرج من ثمن نهائي كأس العالم 2006م بركلة جزاء في الوقت بدل الضائع أمام إيطاليا؟</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>أستراليا</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D321" s="2" t="inlineStr"/>
+      <c r="E321" s="2" t="inlineStr"/>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب أستراليا</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب الأرجنتين الذي طُرد في ربع نهائي كأس العالم 1998م بعد نطحه أحد لاعبي هولندا؟</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>أرييل أورتيغا</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D322" s="2" t="inlineStr"/>
+      <c r="E322" s="2" t="inlineStr"/>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: أورتيغا / أورتيجا / Ariel Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل أول هدف في كأس العالم 2022م من ركلة جزاء؟</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>إينر فالنسيا</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D323" s="2" t="inlineStr"/>
+      <c r="E323" s="2" t="inlineStr"/>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فالنسيا / إنير فالنسيا / Enner Valencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب البرازيل الذي سجل هدفاً عكسياً في المباراة الافتتاحية لكأس العالم 2014م؟</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>مارسيلو فييرا</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D324" s="2" t="inlineStr"/>
+      <c r="E324" s="2" t="inlineStr"/>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: مارسيلو / Marcelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي ارتطمت تسديدته بالقائم في الدقيقة الأخيرة من الوقت الأصلي لنهائي كأس العالم 1978م؟</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>روب رنسنبرينك</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D325" s="2" t="inlineStr"/>
+      <c r="E325" s="2" t="inlineStr"/>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: رنسنبرينك / رينسنبرينك / Rob Rensenbrink</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الأفريقي الذي هزم إسبانيا 3-2 في دور المجموعات بكأس العالم 1998م؟</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>نيجيريا</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D326" s="2" t="inlineStr"/>
+      <c r="E326" s="2" t="inlineStr"/>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب نيجيريا / النسور الممتازة</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الوحيد الذي لم يخسر أي مباراة في كأس العالم 2010م رغم خروجه من الدور الأول؟</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>نيوزيلندا</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D327" s="2" t="inlineStr"/>
+      <c r="E327" s="2" t="inlineStr"/>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب نيوزيلندا / نيوزلندا</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب هولندا الذي افتتح التسجيل بتسديدة من خارج المنطقة في نصف نهائي كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>جيوفاني فان برونكهورست</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D328" s="2" t="inlineStr"/>
+      <c r="E328" s="2" t="inlineStr"/>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: فان برونكهورست / برونكهورست / Giovanni van Bronckhorst</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم المنتخب الذي أقصى إيطاليا من ملحق التصفيات الأوروبية المؤهلة لكأس العالم 2022م؟</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>مقدونيا الشمالية</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D329" s="2" t="inlineStr"/>
+      <c r="E329" s="2" t="inlineStr"/>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: منتخب مقدونيا الشمالية / مقدونيا</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل أول هدف في تاريخ كأس العالم عام 1930م؟</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>لوسيان لوران</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D330" s="2" t="inlineStr"/>
+      <c r="E330" s="2" t="inlineStr"/>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: لوران / Lucien Laurent. سجله في الدقيقة 19 أمام المكسيك</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم مدافع إسبانيا الذي سجل برأسه هدف الفوز على ألمانيا في نصف نهائي كأس العالم 2010م؟</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>كارلوس بويول</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D331" s="2" t="inlineStr"/>
+      <c r="E331" s="2" t="inlineStr"/>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: بويول / كارليس بويول / Carles Puyol</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم اللاعب الذي سجل أول هدف في تاريخ منتخب اليابان في كأس العالم؟</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>ماساشي ناكاياما</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D332" s="2" t="inlineStr"/>
+      <c r="E332" s="2" t="inlineStr"/>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: ناكاياما / Masashi Nakayama. سجله عام 1998م</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم لاعب بلجيكا الذي سجل هدف الفوز في الدقيقة 94 أمام اليابان في ثمن نهائي كأس العالم 2018م؟</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>ناصر الشاذلي</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D333" s="2" t="inlineStr"/>
+      <c r="E333" s="2" t="inlineStr"/>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>يُقبل أيضاً: الشاذلي / ناصر شادلي / Nacer Chadli</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
